--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -9978,7 +9978,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:26:43Z</t>
+          <t>2026-09-13T22:31:14Z</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:26:43Z</t>
+          <t>2026-09-13T22:31:14Z</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:26:43Z</t>
+          <t>2026-09-13T22:31:14Z</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:26:43Z</t>
+          <t>2026-09-13T22:31:14Z</t>
         </is>
       </c>
     </row>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:26:43Z</t>
+          <t>2026-09-13T22:31:14Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -9978,7 +9978,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:14Z</t>
+          <t>2026-09-14T23:16:25Z</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:14Z</t>
+          <t>2026-09-14T23:16:25Z</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:14Z</t>
+          <t>2026-09-14T23:16:25Z</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:14Z</t>
+          <t>2026-09-14T23:16:25Z</t>
         </is>
       </c>
     </row>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:14Z</t>
+          <t>2026-09-14T23:16:25Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L191"/>
+  <dimension ref="A1:L196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10190,6 +10190,266 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="n">
+        <v>126.14190558</v>
+      </c>
+      <c r="E192" s="4" t="n"/>
+      <c r="F192" s="4" t="n"/>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L192" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T23:01:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="n">
+        <v>977.18086211</v>
+      </c>
+      <c r="E193" s="4" t="n"/>
+      <c r="F193" s="4" t="n"/>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H193" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L193" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T23:01:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="n">
+        <v>10.0580554</v>
+      </c>
+      <c r="E194" s="4" t="n"/>
+      <c r="F194" s="4" t="n"/>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J194" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K194" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L194" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T23:01:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="n">
+        <v>17.40618182</v>
+      </c>
+      <c r="E195" s="4" t="n"/>
+      <c r="F195" s="4" t="n"/>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H195" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J195" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L195" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T23:01:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="n">
+        <v>846.5131</v>
+      </c>
+      <c r="E196" s="4" t="n"/>
+      <c r="F196" s="4" t="n"/>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J196" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L196" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T23:01:16Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10450,6 +10450,266 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="n">
+        <v>126.36538776</v>
+      </c>
+      <c r="E197" s="4" t="n"/>
+      <c r="F197" s="4" t="n"/>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L197" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T23:07:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="n">
+        <v>977.67942465</v>
+      </c>
+      <c r="E198" s="4" t="n"/>
+      <c r="F198" s="4" t="n"/>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L198" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T23:07:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="n">
+        <v>10.03011243</v>
+      </c>
+      <c r="E199" s="4" t="n"/>
+      <c r="F199" s="4" t="n"/>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L199" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T23:07:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="n">
+        <v>17.41659982</v>
+      </c>
+      <c r="E200" s="4" t="n"/>
+      <c r="F200" s="4" t="n"/>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L200" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T23:07:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="n">
+        <v>847.4442</v>
+      </c>
+      <c r="E201" s="4" t="n"/>
+      <c r="F201" s="4" t="n"/>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L201" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T23:07:29Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10710,6 +10710,266 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="n">
+        <v>126.51078675</v>
+      </c>
+      <c r="E202" s="4" t="n"/>
+      <c r="F202" s="4" t="n"/>
+      <c r="G202" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K202" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L202" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T22:57:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="n">
+        <v>974.41908397</v>
+      </c>
+      <c r="E203" s="4" t="n"/>
+      <c r="F203" s="4" t="n"/>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L203" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T22:57:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="n">
+        <v>10.04077387</v>
+      </c>
+      <c r="E204" s="4" t="n"/>
+      <c r="F204" s="4" t="n"/>
+      <c r="G204" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J204" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L204" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T22:57:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="n">
+        <v>17.43475009</v>
+      </c>
+      <c r="E205" s="4" t="n"/>
+      <c r="F205" s="4" t="n"/>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H205" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J205" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L205" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T22:57:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="n">
+        <v>848.5458</v>
+      </c>
+      <c r="E206" s="4" t="n"/>
+      <c r="F206" s="4" t="n"/>
+      <c r="G206" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H206" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I206" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J206" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K206" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L206" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T22:57:50Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10970,6 +10970,266 @@
         </is>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="n">
+        <v>126.85739883</v>
+      </c>
+      <c r="E207" s="4" t="n"/>
+      <c r="F207" s="4" t="n"/>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J207" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L207" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T22:43:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="n">
+        <v>974.0930911200001</v>
+      </c>
+      <c r="E208" s="4" t="n"/>
+      <c r="F208" s="4" t="n"/>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J208" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K208" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L208" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T22:43:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="n">
+        <v>10.08929451</v>
+      </c>
+      <c r="E209" s="4" t="n"/>
+      <c r="F209" s="4" t="n"/>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J209" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L209" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T22:43:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="n">
+        <v>17.41962866</v>
+      </c>
+      <c r="E210" s="4" t="n"/>
+      <c r="F210" s="4" t="n"/>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J210" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L210" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T22:43:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="n">
+        <v>849.564</v>
+      </c>
+      <c r="E211" s="4" t="n"/>
+      <c r="F211" s="4" t="n"/>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H211" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J211" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K211" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L211" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T22:43:32Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -11018,7 +11018,7 @@
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:32Z</t>
+          <t>2026-09-19T22:22:51Z</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:32Z</t>
+          <t>2026-09-19T22:22:51Z</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:32Z</t>
+          <t>2026-09-19T22:22:51Z</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:32Z</t>
+          <t>2026-09-19T22:22:51Z</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:32Z</t>
+          <t>2026-09-19T22:22:51Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -11018,7 +11018,7 @@
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:22:51Z</t>
+          <t>2026-09-20T22:35:23Z</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:22:51Z</t>
+          <t>2026-09-20T22:35:23Z</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:22:51Z</t>
+          <t>2026-09-20T22:35:23Z</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:22:51Z</t>
+          <t>2026-09-20T22:35:23Z</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:22:51Z</t>
+          <t>2026-09-20T22:35:23Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:L216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11230,6 +11230,266 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="n">
+        <v>127.32520762</v>
+      </c>
+      <c r="E212" s="4" t="n"/>
+      <c r="F212" s="4" t="n"/>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J212" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L212" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:27:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="n">
+        <v>978.1738505</v>
+      </c>
+      <c r="E213" s="4" t="n"/>
+      <c r="F213" s="4" t="n"/>
+      <c r="G213" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H213" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L213" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:27:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="n">
+        <v>10.16173094</v>
+      </c>
+      <c r="E214" s="4" t="n"/>
+      <c r="F214" s="4" t="n"/>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J214" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L214" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:27:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="n">
+        <v>17.46795112</v>
+      </c>
+      <c r="E215" s="4" t="n"/>
+      <c r="F215" s="4" t="n"/>
+      <c r="G215" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H215" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K215" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L215" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:27:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="n">
+        <v>852.4168</v>
+      </c>
+      <c r="E216" s="4" t="n"/>
+      <c r="F216" s="4" t="n"/>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J216" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K216" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L216" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:27:30Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L216"/>
+  <dimension ref="A1:L221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11490,6 +11490,266 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="n">
+        <v>127.40697118</v>
+      </c>
+      <c r="E217" s="4" t="n"/>
+      <c r="F217" s="4" t="n"/>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J217" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L217" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:07:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="n">
+        <v>976.54829408</v>
+      </c>
+      <c r="E218" s="4" t="n"/>
+      <c r="F218" s="4" t="n"/>
+      <c r="G218" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J218" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K218" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L218" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:07:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="n">
+        <v>10.12553178</v>
+      </c>
+      <c r="E219" s="4" t="n"/>
+      <c r="F219" s="4" t="n"/>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J219" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K219" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L219" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:07:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="n">
+        <v>17.48432964</v>
+      </c>
+      <c r="E220" s="4" t="n"/>
+      <c r="F220" s="4" t="n"/>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J220" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K220" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L220" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:07:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="n">
+        <v>853.4992999999999</v>
+      </c>
+      <c r="E221" s="4" t="n"/>
+      <c r="F221" s="4" t="n"/>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H221" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J221" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K221" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L221" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:07:42Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L221"/>
+  <dimension ref="A1:L226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11750,6 +11750,266 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="n">
+        <v>127.32854992</v>
+      </c>
+      <c r="E222" s="4" t="n"/>
+      <c r="F222" s="4" t="n"/>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J222" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K222" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L222" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T23:02:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="n">
+        <v>974.06298408</v>
+      </c>
+      <c r="E223" s="4" t="n"/>
+      <c r="F223" s="4" t="n"/>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I223" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K223" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L223" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T23:02:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="n">
+        <v>10.10840766</v>
+      </c>
+      <c r="E224" s="4" t="n"/>
+      <c r="F224" s="4" t="n"/>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L224" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T23:02:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="n">
+        <v>17.4978846</v>
+      </c>
+      <c r="E225" s="4" t="n"/>
+      <c r="F225" s="4" t="n"/>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H225" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J225" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K225" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L225" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T23:02:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="n">
+        <v>854.4637</v>
+      </c>
+      <c r="E226" s="4" t="n"/>
+      <c r="F226" s="4" t="n"/>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J226" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K226" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L226" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T23:02:18Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L226"/>
+  <dimension ref="A1:L231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12010,6 +12010,266 @@
         </is>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="n">
+        <v>127.50149009</v>
+      </c>
+      <c r="E227" s="4" t="n"/>
+      <c r="F227" s="4" t="n"/>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H227" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J227" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K227" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L227" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:17:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="n">
+        <v>972.648677</v>
+      </c>
+      <c r="E228" s="4" t="n"/>
+      <c r="F228" s="4" t="n"/>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J228" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L228" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:17:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="n">
+        <v>10.0676244</v>
+      </c>
+      <c r="E229" s="4" t="n"/>
+      <c r="F229" s="4" t="n"/>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I229" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J229" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K229" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L229" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:17:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="n">
+        <v>17.54485339</v>
+      </c>
+      <c r="E230" s="4" t="n"/>
+      <c r="F230" s="4" t="n"/>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H230" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K230" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L230" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:17:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="n">
+        <v>855.6625</v>
+      </c>
+      <c r="E231" s="4" t="n"/>
+      <c r="F231" s="4" t="n"/>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H231" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J231" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K231" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L231" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:17:40Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L231"/>
+  <dimension ref="A1:L236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12270,6 +12270,266 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="n">
+        <v>127.67692147</v>
+      </c>
+      <c r="E232" s="4" t="n"/>
+      <c r="F232" s="4" t="n"/>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I232" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J232" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K232" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L232" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="n">
+        <v>976.9009114200001</v>
+      </c>
+      <c r="E233" s="4" t="n"/>
+      <c r="F233" s="4" t="n"/>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H233" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I233" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K233" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L233" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="n">
+        <v>10.17876014</v>
+      </c>
+      <c r="E234" s="4" t="n"/>
+      <c r="F234" s="4" t="n"/>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K234" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L234" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="n">
+        <v>17.50348841</v>
+      </c>
+      <c r="E235" s="4" t="n"/>
+      <c r="F235" s="4" t="n"/>
+      <c r="G235" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H235" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I235" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J235" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K235" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L235" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="n">
+        <v>857.0058</v>
+      </c>
+      <c r="E236" s="4" t="n"/>
+      <c r="F236" s="4" t="n"/>
+      <c r="G236" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I236" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J236" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K236" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L236" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:23:20Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -12318,7 +12318,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:20Z</t>
+          <t>2026-09-26T23:03:28Z</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:20Z</t>
+          <t>2026-09-26T23:03:28Z</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:20Z</t>
+          <t>2026-09-26T23:03:28Z</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="L235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:20Z</t>
+          <t>2026-09-26T23:03:28Z</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:20Z</t>
+          <t>2026-09-26T23:03:28Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -12318,7 +12318,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:28Z</t>
+          <t>2026-09-27T23:12:47Z</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:28Z</t>
+          <t>2026-09-27T23:12:47Z</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:28Z</t>
+          <t>2026-09-27T23:12:47Z</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="L235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:28Z</t>
+          <t>2026-09-27T23:12:47Z</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:28Z</t>
+          <t>2026-09-27T23:12:47Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L236"/>
+  <dimension ref="A1:L241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12530,6 +12530,266 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="n">
+        <v>127.85591224</v>
+      </c>
+      <c r="E237" s="4" t="n"/>
+      <c r="F237" s="4" t="n"/>
+      <c r="G237" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H237" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I237" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J237" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K237" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L237" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:28:03Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="n">
+        <v>974.71473336</v>
+      </c>
+      <c r="E238" s="4" t="n"/>
+      <c r="F238" s="4" t="n"/>
+      <c r="G238" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I238" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J238" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K238" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L238" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:28:03Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="n">
+        <v>10.15290046</v>
+      </c>
+      <c r="E239" s="4" t="n"/>
+      <c r="F239" s="4" t="n"/>
+      <c r="G239" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H239" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J239" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L239" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:28:03Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="n">
+        <v>17.51451925</v>
+      </c>
+      <c r="E240" s="4" t="n"/>
+      <c r="F240" s="4" t="n"/>
+      <c r="G240" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H240" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I240" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J240" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K240" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L240" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:28:03Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="n">
+        <v>857.8876</v>
+      </c>
+      <c r="E241" s="4" t="n"/>
+      <c r="F241" s="4" t="n"/>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H241" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I241" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J241" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K241" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L241" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:28:03Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L241"/>
+  <dimension ref="A1:L246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12790,6 +12790,266 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="n">
+        <v>128.17051846</v>
+      </c>
+      <c r="E242" s="4" t="n"/>
+      <c r="F242" s="4" t="n"/>
+      <c r="G242" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H242" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J242" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K242" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L242" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:51:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="n">
+        <v>973.30967507</v>
+      </c>
+      <c r="E243" s="4" t="n"/>
+      <c r="F243" s="4" t="n"/>
+      <c r="G243" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H243" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I243" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J243" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K243" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L243" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:51:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="n">
+        <v>10.22815692</v>
+      </c>
+      <c r="E244" s="4" t="n"/>
+      <c r="F244" s="4" t="n"/>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I244" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J244" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K244" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L244" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:51:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="n">
+        <v>17.53314828</v>
+      </c>
+      <c r="E245" s="4" t="n"/>
+      <c r="F245" s="4" t="n"/>
+      <c r="G245" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H245" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J245" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L245" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:51:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="n">
+        <v>859.0629</v>
+      </c>
+      <c r="E246" s="4" t="n"/>
+      <c r="F246" s="4" t="n"/>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J246" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K246" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L246" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T23:51:36Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L246"/>
+  <dimension ref="A1:L251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13050,6 +13050,266 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D247" s="5" t="n">
+        <v>128.30777147</v>
+      </c>
+      <c r="E247" s="4" t="n"/>
+      <c r="F247" s="4" t="n"/>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H247" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J247" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K247" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L247" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:01:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="n">
+        <v>976.84087593</v>
+      </c>
+      <c r="E248" s="4" t="n"/>
+      <c r="F248" s="4" t="n"/>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J248" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L248" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:01:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="n">
+        <v>10.30157462</v>
+      </c>
+      <c r="E249" s="4" t="n"/>
+      <c r="F249" s="4" t="n"/>
+      <c r="G249" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H249" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I249" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J249" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K249" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L249" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:01:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="n">
+        <v>17.54840587</v>
+      </c>
+      <c r="E250" s="4" t="n"/>
+      <c r="F250" s="4" t="n"/>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J250" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K250" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L250" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:01:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="n">
+        <v>860.1753</v>
+      </c>
+      <c r="E251" s="4" t="n"/>
+      <c r="F251" s="4" t="n"/>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J251" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K251" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L251" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:01:59Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L251"/>
+  <dimension ref="A1:L256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13310,6 +13310,266 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="n">
+        <v>129.24489917</v>
+      </c>
+      <c r="E252" s="4" t="n"/>
+      <c r="F252" s="4" t="n"/>
+      <c r="G252" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J252" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K252" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L252" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="n">
+        <v>973.92813268</v>
+      </c>
+      <c r="E253" s="4" t="n"/>
+      <c r="F253" s="4" t="n"/>
+      <c r="G253" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H253" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J253" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K253" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L253" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="n">
+        <v>10.37922146</v>
+      </c>
+      <c r="E254" s="4" t="n"/>
+      <c r="F254" s="4" t="n"/>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J254" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K254" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L254" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v>17.67424576</v>
+      </c>
+      <c r="E255" s="4" t="n"/>
+      <c r="F255" s="4" t="n"/>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J255" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K255" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L255" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="n">
+        <v>866.5612</v>
+      </c>
+      <c r="E256" s="4" t="n"/>
+      <c r="F256" s="4" t="n"/>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I256" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J256" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K256" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L256" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:04Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L256"/>
+  <dimension ref="A1:L261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13570,6 +13570,266 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="n">
+        <v>129.97746121</v>
+      </c>
+      <c r="E257" s="4" t="n"/>
+      <c r="F257" s="4" t="n"/>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J257" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K257" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L257" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T23:55:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="n">
+        <v>981.17880877</v>
+      </c>
+      <c r="E258" s="4" t="n"/>
+      <c r="F258" s="4" t="n"/>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J258" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K258" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L258" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T23:55:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="n">
+        <v>10.39904073</v>
+      </c>
+      <c r="E259" s="4" t="n"/>
+      <c r="F259" s="4" t="n"/>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H259" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I259" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J259" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K259" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L259" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T23:55:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="n">
+        <v>17.73255527</v>
+      </c>
+      <c r="E260" s="4" t="n"/>
+      <c r="F260" s="4" t="n"/>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I260" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J260" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K260" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L260" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T23:55:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="n">
+        <v>871.3689000000001</v>
+      </c>
+      <c r="E261" s="4" t="n"/>
+      <c r="F261" s="4" t="n"/>
+      <c r="G261" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H261" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J261" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K261" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L261" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T23:55:13Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -13618,7 +13618,7 @@
       </c>
       <c r="L257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:13Z</t>
+          <t>2026-10-03T23:13:52Z</t>
         </is>
       </c>
     </row>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:13Z</t>
+          <t>2026-10-03T23:13:52Z</t>
         </is>
       </c>
     </row>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="L259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:13Z</t>
+          <t>2026-10-03T23:13:52Z</t>
         </is>
       </c>
     </row>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:13Z</t>
+          <t>2026-10-03T23:13:52Z</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
       </c>
       <c r="L261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:13Z</t>
+          <t>2026-10-03T23:13:52Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -13618,7 +13618,7 @@
       </c>
       <c r="L257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:13:52Z</t>
+          <t>2026-10-04T23:25:00Z</t>
         </is>
       </c>
     </row>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:13:52Z</t>
+          <t>2026-10-04T23:25:00Z</t>
         </is>
       </c>
     </row>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="L259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:13:52Z</t>
+          <t>2026-10-04T23:25:00Z</t>
         </is>
       </c>
     </row>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:13:52Z</t>
+          <t>2026-10-04T23:25:00Z</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
       </c>
       <c r="L261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:13:52Z</t>
+          <t>2026-10-04T23:25:00Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L261"/>
+  <dimension ref="A1:L266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13830,6 +13830,266 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="n">
+        <v>130.13017601</v>
+      </c>
+      <c r="E262" s="4" t="n"/>
+      <c r="F262" s="4" t="n"/>
+      <c r="G262" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I262" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J262" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K262" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L262" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T01:21:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="n">
+        <v>977.21940683</v>
+      </c>
+      <c r="E263" s="4" t="n"/>
+      <c r="F263" s="4" t="n"/>
+      <c r="G263" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H263" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J263" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K263" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L263" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T01:21:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="n">
+        <v>10.22854613</v>
+      </c>
+      <c r="E264" s="4" t="n"/>
+      <c r="F264" s="4" t="n"/>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I264" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J264" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K264" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L264" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T01:21:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="n">
+        <v>17.74907713</v>
+      </c>
+      <c r="E265" s="4" t="n"/>
+      <c r="F265" s="4" t="n"/>
+      <c r="G265" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H265" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I265" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J265" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K265" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L265" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T01:21:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="n">
+        <v>872.3927</v>
+      </c>
+      <c r="E266" s="4" t="n"/>
+      <c r="F266" s="4" t="n"/>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I266" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J266" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K266" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L266" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T01:21:57Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L266"/>
+  <dimension ref="A1:L271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14090,6 +14090,266 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="n">
+        <v>130.3403684</v>
+      </c>
+      <c r="E267" s="4" t="n"/>
+      <c r="F267" s="4" t="n"/>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H267" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I267" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J267" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L267" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:56:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="n">
+        <v>984.2626181099999</v>
+      </c>
+      <c r="E268" s="4" t="n"/>
+      <c r="F268" s="4" t="n"/>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I268" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J268" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K268" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L268" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:56:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="n">
+        <v>10.22986756</v>
+      </c>
+      <c r="E269" s="4" t="n"/>
+      <c r="F269" s="4" t="n"/>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H269" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J269" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K269" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L269" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:56:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="n">
+        <v>17.7701205</v>
+      </c>
+      <c r="E270" s="4" t="n"/>
+      <c r="F270" s="4" t="n"/>
+      <c r="G270" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J270" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L270" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:56:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="n">
+        <v>873.867</v>
+      </c>
+      <c r="E271" s="4" t="n"/>
+      <c r="F271" s="4" t="n"/>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H271" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I271" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J271" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K271" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L271" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:56:40Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L271"/>
+  <dimension ref="A1:L276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14350,6 +14350,266 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D272" s="5" t="n">
+        <v>130.46356341</v>
+      </c>
+      <c r="E272" s="4" t="n"/>
+      <c r="F272" s="4" t="n"/>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I272" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J272" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K272" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L272" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:17:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="n">
+        <v>979.0788922</v>
+      </c>
+      <c r="E273" s="4" t="n"/>
+      <c r="F273" s="4" t="n"/>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J273" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K273" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L273" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:17:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D274" s="5" t="n">
+        <v>10.22960031</v>
+      </c>
+      <c r="E274" s="4" t="n"/>
+      <c r="F274" s="4" t="n"/>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J274" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K274" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L274" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:17:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>17.7819991</v>
+      </c>
+      <c r="E275" s="4" t="n"/>
+      <c r="F275" s="4" t="n"/>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H275" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I275" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J275" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K275" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L275" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:17:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>874.7320999999999</v>
+      </c>
+      <c r="E276" s="4" t="n"/>
+      <c r="F276" s="4" t="n"/>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I276" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J276" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K276" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L276" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:17:57Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L276"/>
+  <dimension ref="A1:L281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14610,6 +14610,266 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>130.66290139</v>
+      </c>
+      <c r="E277" s="4" t="n"/>
+      <c r="F277" s="4" t="n"/>
+      <c r="G277" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H277" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I277" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J277" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K277" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L277" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:31:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>980.61472543</v>
+      </c>
+      <c r="E278" s="4" t="n"/>
+      <c r="F278" s="4" t="n"/>
+      <c r="G278" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I278" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J278" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K278" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L278" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:31:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>10.266129</v>
+      </c>
+      <c r="E279" s="4" t="n"/>
+      <c r="F279" s="4" t="n"/>
+      <c r="G279" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H279" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I279" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J279" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L279" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:31:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="n">
+        <v>17.79357915</v>
+      </c>
+      <c r="E280" s="4" t="n"/>
+      <c r="F280" s="4" t="n"/>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H280" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I280" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J280" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K280" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L280" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:31:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="n">
+        <v>875.6505</v>
+      </c>
+      <c r="E281" s="4" t="n"/>
+      <c r="F281" s="4" t="n"/>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I281" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J281" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K281" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L281" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:31:47Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L281"/>
+  <dimension ref="A1:L286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14870,6 +14870,266 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="n">
+        <v>131.03154748</v>
+      </c>
+      <c r="E282" s="4" t="n"/>
+      <c r="F282" s="4" t="n"/>
+      <c r="G282" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H282" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I282" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J282" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K282" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L282" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:11:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="n">
+        <v>982.00454402</v>
+      </c>
+      <c r="E283" s="4" t="n"/>
+      <c r="F283" s="4" t="n"/>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H283" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J283" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L283" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:11:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D284" s="5" t="n">
+        <v>10.33956995</v>
+      </c>
+      <c r="E284" s="4" t="n"/>
+      <c r="F284" s="4" t="n"/>
+      <c r="G284" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H284" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I284" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J284" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K284" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L284" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:11:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="n">
+        <v>17.7698026</v>
+      </c>
+      <c r="E285" s="4" t="n"/>
+      <c r="F285" s="4" t="n"/>
+      <c r="G285" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H285" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I285" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J285" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K285" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L285" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:11:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D286" s="5" t="n">
+        <v>876.7976</v>
+      </c>
+      <c r="E286" s="4" t="n"/>
+      <c r="F286" s="4" t="n"/>
+      <c r="G286" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H286" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J286" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K286" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L286" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:11:09Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -14918,7 +14918,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:09Z</t>
+          <t>2026-10-10T23:42:06Z</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="L283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:09Z</t>
+          <t>2026-10-10T23:42:06Z</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:09Z</t>
+          <t>2026-10-10T23:42:06Z</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="L285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:09Z</t>
+          <t>2026-10-10T23:42:06Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:09Z</t>
+          <t>2026-10-10T23:42:06Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -14918,7 +14918,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:06Z</t>
+          <t>2026-10-11T23:48:53Z</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="L283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:06Z</t>
+          <t>2026-10-11T23:48:53Z</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:06Z</t>
+          <t>2026-10-11T23:48:53Z</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="L285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:06Z</t>
+          <t>2026-10-11T23:48:53Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:06Z</t>
+          <t>2026-10-11T23:48:53Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -14918,7 +14918,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:48:53Z</t>
+          <t>2026-10-13T02:10:06Z</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="L283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:48:53Z</t>
+          <t>2026-10-13T02:10:06Z</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:48:53Z</t>
+          <t>2026-10-13T02:10:06Z</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="L285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:48:53Z</t>
+          <t>2026-10-13T02:10:06Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:48:53Z</t>
+          <t>2026-10-13T02:10:06Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L286"/>
+  <dimension ref="A1:L291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15130,6 +15130,266 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="n">
+        <v>131.163315</v>
+      </c>
+      <c r="E287" s="4" t="n"/>
+      <c r="F287" s="4" t="n"/>
+      <c r="G287" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H287" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I287" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J287" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K287" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L287" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:47:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D288" s="5" t="n">
+        <v>982.75895071</v>
+      </c>
+      <c r="E288" s="4" t="n"/>
+      <c r="F288" s="4" t="n"/>
+      <c r="G288" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H288" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I288" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J288" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K288" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L288" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:47:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="n">
+        <v>10.49620157</v>
+      </c>
+      <c r="E289" s="4" t="n"/>
+      <c r="F289" s="4" t="n"/>
+      <c r="G289" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H289" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I289" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J289" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K289" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L289" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:47:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="n">
+        <v>17.78368179</v>
+      </c>
+      <c r="E290" s="4" t="n"/>
+      <c r="F290" s="4" t="n"/>
+      <c r="G290" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H290" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I290" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J290" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K290" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L290" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:47:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="n">
+        <v>877.9023</v>
+      </c>
+      <c r="E291" s="4" t="n"/>
+      <c r="F291" s="4" t="n"/>
+      <c r="G291" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H291" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I291" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J291" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K291" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L291" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13T23:47:44Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L291"/>
+  <dimension ref="A1:L296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15390,6 +15390,266 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D292" s="5" t="n">
+        <v>131.36720909</v>
+      </c>
+      <c r="E292" s="4" t="n"/>
+      <c r="F292" s="4" t="n"/>
+      <c r="G292" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H292" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I292" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J292" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K292" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L292" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:20:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="n">
+        <v>977.68092347</v>
+      </c>
+      <c r="E293" s="4" t="n"/>
+      <c r="F293" s="4" t="n"/>
+      <c r="G293" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H293" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I293" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J293" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K293" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L293" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:20:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="n">
+        <v>10.48211611</v>
+      </c>
+      <c r="E294" s="4" t="n"/>
+      <c r="F294" s="4" t="n"/>
+      <c r="G294" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H294" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I294" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J294" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K294" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L294" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:20:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="n">
+        <v>17.80086663</v>
+      </c>
+      <c r="E295" s="4" t="n"/>
+      <c r="F295" s="4" t="n"/>
+      <c r="G295" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H295" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I295" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J295" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K295" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L295" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:20:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="n">
+        <v>879.1224999999999</v>
+      </c>
+      <c r="E296" s="4" t="n"/>
+      <c r="F296" s="4" t="n"/>
+      <c r="G296" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H296" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I296" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J296" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K296" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L296" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:20:39Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L296"/>
+  <dimension ref="A1:L301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15650,6 +15650,266 @@
         </is>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="n">
+        <v>131.5490703</v>
+      </c>
+      <c r="E297" s="4" t="n"/>
+      <c r="F297" s="4" t="n"/>
+      <c r="G297" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H297" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I297" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J297" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K297" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L297" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:09:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="n">
+        <v>985.729808</v>
+      </c>
+      <c r="E298" s="4" t="n"/>
+      <c r="F298" s="4" t="n"/>
+      <c r="G298" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H298" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I298" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K298" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L298" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:09:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="n">
+        <v>10.49431116</v>
+      </c>
+      <c r="E299" s="4" t="n"/>
+      <c r="F299" s="4" t="n"/>
+      <c r="G299" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H299" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I299" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J299" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K299" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L299" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:09:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D300" s="5" t="n">
+        <v>17.81200087</v>
+      </c>
+      <c r="E300" s="4" t="n"/>
+      <c r="F300" s="4" t="n"/>
+      <c r="G300" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H300" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I300" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K300" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L300" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:09:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D301" s="5" t="n">
+        <v>880.1159</v>
+      </c>
+      <c r="E301" s="4" t="n"/>
+      <c r="F301" s="4" t="n"/>
+      <c r="G301" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H301" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I301" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K301" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L301" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:09:26Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L301"/>
+  <dimension ref="A1:L306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15910,6 +15910,266 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D302" s="5" t="n">
+        <v>131.78568864</v>
+      </c>
+      <c r="E302" s="4" t="n"/>
+      <c r="F302" s="4" t="n"/>
+      <c r="G302" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H302" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I302" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K302" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L302" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T22:56:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="n">
+        <v>991.16445734</v>
+      </c>
+      <c r="E303" s="4" t="n"/>
+      <c r="F303" s="4" t="n"/>
+      <c r="G303" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H303" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I303" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J303" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K303" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L303" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T22:56:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="n">
+        <v>10.60651703</v>
+      </c>
+      <c r="E304" s="4" t="n"/>
+      <c r="F304" s="4" t="n"/>
+      <c r="G304" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H304" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I304" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J304" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K304" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L304" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T22:56:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="n">
+        <v>17.79159714</v>
+      </c>
+      <c r="E305" s="4" t="n"/>
+      <c r="F305" s="4" t="n"/>
+      <c r="G305" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H305" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I305" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J305" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K305" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L305" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T22:56:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D306" s="5" t="n">
+        <v>881.0664</v>
+      </c>
+      <c r="E306" s="4" t="n"/>
+      <c r="F306" s="4" t="n"/>
+      <c r="G306" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H306" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I306" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J306" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K306" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L306" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T22:56:11Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -15958,7 +15958,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:11Z</t>
+          <t>2026-10-17T22:29:57Z</t>
         </is>
       </c>
     </row>
@@ -16010,7 +16010,7 @@
       </c>
       <c r="L303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:11Z</t>
+          <t>2026-10-17T22:29:57Z</t>
         </is>
       </c>
     </row>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:11Z</t>
+          <t>2026-10-17T22:29:57Z</t>
         </is>
       </c>
     </row>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="L305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:11Z</t>
+          <t>2026-10-17T22:29:57Z</t>
         </is>
       </c>
     </row>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:11Z</t>
+          <t>2026-10-17T22:29:57Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -15958,7 +15958,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:29:57Z</t>
+          <t>2026-10-18T22:30:58Z</t>
         </is>
       </c>
     </row>
@@ -16010,7 +16010,7 @@
       </c>
       <c r="L303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:29:57Z</t>
+          <t>2026-10-18T22:30:58Z</t>
         </is>
       </c>
     </row>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:29:57Z</t>
+          <t>2026-10-18T22:30:58Z</t>
         </is>
       </c>
     </row>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="L305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:29:57Z</t>
+          <t>2026-10-18T22:30:58Z</t>
         </is>
       </c>
     </row>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:29:57Z</t>
+          <t>2026-10-18T22:30:58Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L306"/>
+  <dimension ref="A1:L311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16170,6 +16170,266 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="n">
+        <v>132.01552371</v>
+      </c>
+      <c r="E307" s="4" t="n"/>
+      <c r="F307" s="4" t="n"/>
+      <c r="G307" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H307" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I307" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J307" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K307" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L307" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:50:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D308" s="5" t="n">
+        <v>988.97203073</v>
+      </c>
+      <c r="E308" s="4" t="n"/>
+      <c r="F308" s="4" t="n"/>
+      <c r="G308" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H308" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I308" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J308" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K308" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L308" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:50:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C309" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D309" s="5" t="n">
+        <v>10.65261701</v>
+      </c>
+      <c r="E309" s="4" t="n"/>
+      <c r="F309" s="4" t="n"/>
+      <c r="G309" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H309" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I309" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J309" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K309" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L309" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:50:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D310" s="5" t="n">
+        <v>17.79811257</v>
+      </c>
+      <c r="E310" s="4" t="n"/>
+      <c r="F310" s="4" t="n"/>
+      <c r="G310" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H310" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I310" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J310" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K310" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L310" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:50:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D311" s="5" t="n">
+        <v>881.8769</v>
+      </c>
+      <c r="E311" s="4" t="n"/>
+      <c r="F311" s="4" t="n"/>
+      <c r="G311" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H311" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I311" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J311" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K311" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L311" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:50:23Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L311"/>
+  <dimension ref="A1:L316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16430,6 +16430,266 @@
         </is>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D312" s="5" t="n">
+        <v>132.29644771</v>
+      </c>
+      <c r="E312" s="4" t="n"/>
+      <c r="F312" s="4" t="n"/>
+      <c r="G312" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H312" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I312" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J312" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K312" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L312" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T23:16:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="n">
+        <v>993.1759582</v>
+      </c>
+      <c r="E313" s="4" t="n"/>
+      <c r="F313" s="4" t="n"/>
+      <c r="G313" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H313" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I313" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J313" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K313" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L313" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T23:16:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D314" s="5" t="n">
+        <v>10.71562712</v>
+      </c>
+      <c r="E314" s="4" t="n"/>
+      <c r="F314" s="4" t="n"/>
+      <c r="G314" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H314" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I314" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J314" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K314" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L314" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T23:16:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B315" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="n">
+        <v>17.82007379</v>
+      </c>
+      <c r="E315" s="4" t="n"/>
+      <c r="F315" s="4" t="n"/>
+      <c r="G315" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H315" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I315" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J315" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K315" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L315" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T23:16:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C316" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="n">
+        <v>883.3963</v>
+      </c>
+      <c r="E316" s="4" t="n"/>
+      <c r="F316" s="4" t="n"/>
+      <c r="G316" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H316" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I316" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J316" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K316" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L316" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T23:16:39Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L316"/>
+  <dimension ref="A1:L321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16690,6 +16690,266 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="n">
+        <v>132.54477086</v>
+      </c>
+      <c r="E317" s="4" t="n"/>
+      <c r="F317" s="4" t="n"/>
+      <c r="G317" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H317" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I317" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J317" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K317" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L317" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T23:29:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C318" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="n">
+        <v>993.21105346</v>
+      </c>
+      <c r="E318" s="4" t="n"/>
+      <c r="F318" s="4" t="n"/>
+      <c r="G318" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H318" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I318" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J318" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K318" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L318" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T23:29:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C319" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="n">
+        <v>10.80240772</v>
+      </c>
+      <c r="E319" s="4" t="n"/>
+      <c r="F319" s="4" t="n"/>
+      <c r="G319" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H319" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I319" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J319" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K319" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L319" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T23:29:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="n">
+        <v>17.8386646</v>
+      </c>
+      <c r="E320" s="4" t="n"/>
+      <c r="F320" s="4" t="n"/>
+      <c r="G320" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H320" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I320" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J320" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K320" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L320" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T23:29:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="n">
+        <v>884.7496</v>
+      </c>
+      <c r="E321" s="4" t="n"/>
+      <c r="F321" s="4" t="n"/>
+      <c r="G321" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H321" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I321" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J321" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K321" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L321" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T23:29:54Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L321"/>
+  <dimension ref="A1:L326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16950,6 +16950,266 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B322" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="n">
+        <v>132.78202957</v>
+      </c>
+      <c r="E322" s="4" t="n"/>
+      <c r="F322" s="4" t="n"/>
+      <c r="G322" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H322" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I322" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J322" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K322" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L322" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T23:29:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="n">
+        <v>993.08836371</v>
+      </c>
+      <c r="E323" s="4" t="n"/>
+      <c r="F323" s="4" t="n"/>
+      <c r="G323" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H323" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I323" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J323" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K323" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L323" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T23:29:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B324" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="n">
+        <v>10.85596986</v>
+      </c>
+      <c r="E324" s="4" t="n"/>
+      <c r="F324" s="4" t="n"/>
+      <c r="G324" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H324" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I324" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J324" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K324" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L324" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T23:29:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="n">
+        <v>17.85783286</v>
+      </c>
+      <c r="E325" s="4" t="n"/>
+      <c r="F325" s="4" t="n"/>
+      <c r="G325" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H325" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I325" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J325" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K325" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L325" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T23:29:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B326" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D326" s="5" t="n">
+        <v>886.2271</v>
+      </c>
+      <c r="E326" s="4" t="n"/>
+      <c r="F326" s="4" t="n"/>
+      <c r="G326" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H326" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I326" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J326" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K326" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L326" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T23:29:13Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L326"/>
+  <dimension ref="A1:L331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17210,6 +17210,266 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D327" s="5" t="n">
+        <v>133.03476918</v>
+      </c>
+      <c r="E327" s="4" t="n"/>
+      <c r="F327" s="4" t="n"/>
+      <c r="G327" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H327" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I327" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J327" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K327" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L327" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:17:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D328" s="5" t="n">
+        <v>994.03555758</v>
+      </c>
+      <c r="E328" s="4" t="n"/>
+      <c r="F328" s="4" t="n"/>
+      <c r="G328" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H328" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I328" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J328" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K328" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L328" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:17:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D329" s="5" t="n">
+        <v>11.00248494</v>
+      </c>
+      <c r="E329" s="4" t="n"/>
+      <c r="F329" s="4" t="n"/>
+      <c r="G329" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H329" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I329" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J329" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K329" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L329" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:17:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D330" s="5" t="n">
+        <v>17.8400822</v>
+      </c>
+      <c r="E330" s="4" t="n"/>
+      <c r="F330" s="4" t="n"/>
+      <c r="G330" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H330" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I330" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J330" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K330" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L330" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:17:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D331" s="5" t="n">
+        <v>887.302</v>
+      </c>
+      <c r="E331" s="4" t="n"/>
+      <c r="F331" s="4" t="n"/>
+      <c r="G331" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H331" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I331" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J331" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K331" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L331" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:17:56Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -17258,7 +17258,7 @@
       </c>
       <c r="L327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:17:56Z</t>
+          <t>2026-10-24T22:37:05Z</t>
         </is>
       </c>
     </row>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:17:56Z</t>
+          <t>2026-10-24T22:37:05Z</t>
         </is>
       </c>
     </row>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="L329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:17:56Z</t>
+          <t>2026-10-24T22:37:05Z</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:17:56Z</t>
+          <t>2026-10-24T22:37:05Z</t>
         </is>
       </c>
     </row>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="L331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:17:56Z</t>
+          <t>2026-10-24T22:37:05Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -17258,7 +17258,7 @@
       </c>
       <c r="L327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:05Z</t>
+          <t>2026-10-25T22:43:39Z</t>
         </is>
       </c>
     </row>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:05Z</t>
+          <t>2026-10-25T22:43:39Z</t>
         </is>
       </c>
     </row>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="L329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:05Z</t>
+          <t>2026-10-25T22:43:39Z</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:05Z</t>
+          <t>2026-10-25T22:43:39Z</t>
         </is>
       </c>
     </row>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="L331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:05Z</t>
+          <t>2026-10-25T22:43:39Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -17258,7 +17258,7 @@
       </c>
       <c r="L327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:39Z</t>
+          <t>2026-10-26T23:58:32Z</t>
         </is>
       </c>
     </row>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:39Z</t>
+          <t>2026-10-26T23:58:32Z</t>
         </is>
       </c>
     </row>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="L329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:39Z</t>
+          <t>2026-10-26T23:58:32Z</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:39Z</t>
+          <t>2026-10-26T23:58:32Z</t>
         </is>
       </c>
     </row>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="L331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:39Z</t>
+          <t>2026-10-26T23:58:32Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L331"/>
+  <dimension ref="A1:L336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17470,6 +17470,266 @@
         </is>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B332" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D332" s="5" t="n">
+        <v>133.22107552</v>
+      </c>
+      <c r="E332" s="4" t="n"/>
+      <c r="F332" s="4" t="n"/>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H332" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I332" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J332" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K332" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L332" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T23:53:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D333" s="5" t="n">
+        <v>989.71903352</v>
+      </c>
+      <c r="E333" s="4" t="n"/>
+      <c r="F333" s="4" t="n"/>
+      <c r="G333" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H333" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I333" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J333" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K333" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L333" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T23:53:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D334" s="5" t="n">
+        <v>11.02567721</v>
+      </c>
+      <c r="E334" s="4" t="n"/>
+      <c r="F334" s="4" t="n"/>
+      <c r="G334" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H334" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I334" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J334" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K334" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L334" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T23:53:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D335" s="5" t="n">
+        <v>17.83932484</v>
+      </c>
+      <c r="E335" s="4" t="n"/>
+      <c r="F335" s="4" t="n"/>
+      <c r="G335" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H335" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I335" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J335" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K335" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L335" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T23:53:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D336" s="5" t="n">
+        <v>888.1183</v>
+      </c>
+      <c r="E336" s="4" t="n"/>
+      <c r="F336" s="4" t="n"/>
+      <c r="G336" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H336" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I336" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J336" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K336" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L336" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T23:53:31Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L336"/>
+  <dimension ref="A1:L341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17730,6 +17730,266 @@
         </is>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D337" s="5" t="n">
+        <v>133.35697247</v>
+      </c>
+      <c r="E337" s="4" t="n"/>
+      <c r="F337" s="4" t="n"/>
+      <c r="G337" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H337" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K337" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L337" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:09:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D338" s="5" t="n">
+        <v>989.38890515</v>
+      </c>
+      <c r="E338" s="4" t="n"/>
+      <c r="F338" s="4" t="n"/>
+      <c r="G338" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H338" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I338" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J338" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K338" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L338" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:09:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B339" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D339" s="5" t="n">
+        <v>11.07381748</v>
+      </c>
+      <c r="E339" s="4" t="n"/>
+      <c r="F339" s="4" t="n"/>
+      <c r="G339" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H339" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I339" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J339" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K339" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L339" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:09:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D340" s="5" t="n">
+        <v>17.83603481</v>
+      </c>
+      <c r="E340" s="4" t="n"/>
+      <c r="F340" s="4" t="n"/>
+      <c r="G340" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H340" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I340" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J340" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K340" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L340" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:09:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D341" s="5" t="n">
+        <v>888.8909</v>
+      </c>
+      <c r="E341" s="4" t="n"/>
+      <c r="F341" s="4" t="n"/>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H341" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I341" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J341" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K341" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L341" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:09:33Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L341"/>
+  <dimension ref="A1:L346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17990,6 +17990,266 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D342" s="5" t="n">
+        <v>133.5117934</v>
+      </c>
+      <c r="E342" s="4" t="n"/>
+      <c r="F342" s="4" t="n"/>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H342" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I342" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J342" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K342" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L342" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:03:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B343" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C343" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D343" s="5" t="n">
+        <v>992.80018713</v>
+      </c>
+      <c r="E343" s="4" t="n"/>
+      <c r="F343" s="4" t="n"/>
+      <c r="G343" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H343" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I343" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J343" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K343" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L343" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:03:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D344" s="5" t="n">
+        <v>10.99880148</v>
+      </c>
+      <c r="E344" s="4" t="n"/>
+      <c r="F344" s="4" t="n"/>
+      <c r="G344" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H344" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I344" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J344" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K344" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L344" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:03:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B345" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D345" s="5" t="n">
+        <v>17.84483981</v>
+      </c>
+      <c r="E345" s="4" t="n"/>
+      <c r="F345" s="4" t="n"/>
+      <c r="G345" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H345" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I345" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J345" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K345" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L345" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:03:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B346" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D346" s="5" t="n">
+        <v>889.2553</v>
+      </c>
+      <c r="E346" s="4" t="n"/>
+      <c r="F346" s="4" t="n"/>
+      <c r="G346" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H346" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I346" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J346" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K346" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L346" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:03:15Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L346"/>
+  <dimension ref="A1:L351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18250,6 +18250,266 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B347" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D347" s="5" t="n">
+        <v>133.71041635</v>
+      </c>
+      <c r="E347" s="4" t="n"/>
+      <c r="F347" s="4" t="n"/>
+      <c r="G347" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H347" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I347" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J347" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K347" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L347" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T23:56:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B348" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D348" s="5" t="n">
+        <v>991.25386822</v>
+      </c>
+      <c r="E348" s="4" t="n"/>
+      <c r="F348" s="4" t="n"/>
+      <c r="G348" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H348" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I348" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J348" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K348" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L348" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T23:56:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B349" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D349" s="5" t="n">
+        <v>11.01676834</v>
+      </c>
+      <c r="E349" s="4" t="n"/>
+      <c r="F349" s="4" t="n"/>
+      <c r="G349" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H349" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I349" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J349" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K349" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L349" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T23:56:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B350" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D350" s="5" t="n">
+        <v>17.81048685</v>
+      </c>
+      <c r="E350" s="4" t="n"/>
+      <c r="F350" s="4" t="n"/>
+      <c r="G350" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H350" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I350" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J350" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K350" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L350" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T23:56:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B351" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D351" s="5" t="n">
+        <v>889.5753999999999</v>
+      </c>
+      <c r="E351" s="4" t="n"/>
+      <c r="F351" s="4" t="n"/>
+      <c r="G351" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H351" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I351" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J351" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K351" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L351" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T23:56:05Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
